--- a/docs/OXar_Treatment_Type_Templates.xlsx
+++ b/docs/OXar_Treatment_Type_Templates.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,7 +46,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -68,6 +68,24 @@
     <font>
       <b val="1"/>
       <color rgb="002F7D76"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C9821C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002F7D76"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -133,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -160,20 +178,33 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -541,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -554,14 +585,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OX.ar — Treatment-Type Templates</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="44" customHeight="1">
+          <t>OX.ar — Treatment-Type Templates (UI binding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>One tab per treatment type = the template definition that drives the Treatment Planning UI. Change the treatment type and the planning page shows exactly these sections/fields/tabs/steps. Synthetic test couple. Independent of OX.gp.</t>
+          <t>One tab per treatment type = the template that drives the Treatment Planning UI. Each field carries its Entity, Attribute (logical name), Data type, Control and Relationship so it can be bound directly. Machine-readable copy: treatment-type-templates.ui.json. Synthetic test couple. Independent of OX.gp.</t>
         </is>
       </c>
     </row>
@@ -829,9 +860,23 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Src legend:</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>code = attribute confirmed in OxArBackendReact  ·  form = from the cycle form (confirm logical name)  ·  new = new Embryo-Module entity/field</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -843,19 +888,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>IVF — Template Definition</t>
+          <t>IVF — Template Definition (UI binding)</t>
         </is>
       </c>
     </row>
@@ -876,11 +927,11 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Plan steps (seeds the worklist):</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>Plan steps (seed the worklist):</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Consent &amp; 3PC  →  Stimulation  →  Folliculogram  →  Trigger  →  OPU  →  Semen Prep  →  Insemination (ICSI)  →  Fertilisation  →  Culture D2-7  →  Transfer  →  Freeze surplus  →  Outcome</t>
@@ -895,17 +946,47 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Field shown</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Sample value (test couple)</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t>Attribute (logical)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Data type</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Relationship / Option set</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t>Required</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Sample value</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Src</t>
         </is>
       </c>
     </row>
@@ -920,14 +1001,44 @@
           <t>Treatment Name</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_name</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Textbox</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>IVF — Antagonist protocol</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -938,14 +1049,44 @@
           <t>Treatment Type</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmenttype</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet: bcrm_treatmenttype</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>IVF</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -956,12 +1097,42 @@
           <t>Cycle Sequence No</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_cyclesequencenumber</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>AutoNumber</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Read-only</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>CY-1183</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -970,14 +1141,44 @@
           <t>Billing Option</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmentbillingoption</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Self-funded</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
@@ -988,12 +1189,42 @@
           <t>ANZARD Cycle Type</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_anzardcycletype</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Stimulated — fresh</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr"/>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr"/>
@@ -1002,12 +1233,42 @@
           <t>Treatment Template</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmenttemplate</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_eventtemplate</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Standard ICSI, Day 5</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr"/>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -1020,14 +1281,44 @@
           <t>Patient</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_patient</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; contact</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Priya Sample (DEMO) · NHR-0042 · F · DOB 12 Mar 1991</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1329,42 @@
           <t>Partner</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_partner</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; contact</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Alex Sample (DEMO) · NHR-0043 · M · DOB 04 Aug 1988</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr"/>
@@ -1052,14 +1373,44 @@
           <t>Cycle Doctor</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_cycledoctor</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; systemuser/bcrm_staff</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Dr M. Osei</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1421,42 @@
           <t>Cycle Nurse</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_cyclenurse</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; systemuser/bcrm_staff</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>R. Nolan</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr"/>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
@@ -1084,19 +1465,49 @@
           <t>Patient RX Group</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_patientrxgroup</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Group B</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Clinic &amp; Dates</t>
         </is>
@@ -1106,12 +1517,42 @@
           <t>Managing Clinic</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_managingclinic</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; account/bcrm_clinic</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>OX.ar City (DEMO)</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr"/>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr"/>
@@ -1120,12 +1561,42 @@
           <t>Procedure Clinic</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_procedureclinic</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; account/bcrm_clinic</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>OX.ar City Lab</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr"/>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr"/>
@@ -1134,12 +1605,42 @@
           <t>Expected Start</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_expectedstartdate</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>14 Jul 2026</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr"/>
+      <c r="J22" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr"/>
@@ -1148,12 +1649,42 @@
           <t>First Injection</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_firstinjectiondate</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>1:1 stim detail</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>16 Jul 2026</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr"/>
@@ -1162,12 +1693,42 @@
           <t>Expected OPU</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_expectedtreatmentdate</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>28 Jul 2026</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
+      <c r="J24" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -1180,12 +1741,42 @@
           <t>Female Diagnosis</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_details_diagnosis</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>OptionSet / Lookup</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>Tubal factor</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr"/>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr"/>
@@ -1194,12 +1785,42 @@
           <t>Male Diagnosis</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_details_sec_diagnosis</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet / Lookup</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Mild oligospermia</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr"/>
@@ -1208,15 +1829,45 @@
           <t>Comment</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_details_other_diagnosis</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Multiline Text</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Textarea</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
@@ -1226,12 +1877,42 @@
           <t>Event Template</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_eventtemplate</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_eventtemplate (ApplyToCycle seeds events)</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>IVF Standard</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr"/>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr"/>
@@ -1240,12 +1921,42 @@
           <t>Research Project</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_researchproject</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_researchproject</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>PROTO time-lapse study</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr"/>
+      <c r="J29" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr"/>
@@ -1254,12 +1965,42 @@
           <t>Sperm Source</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_spermsource</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>Partner (fresh)</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr"/>
@@ -1268,12 +2009,42 @@
           <t>Insemination Method</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_insemination</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_method</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>OptionSet (IVF/ICSI)</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>ICSI</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr"/>
+      <c r="J31" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr"/>
@@ -1282,174 +2053,269 @@
           <t>No. Embryos to Replace</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_no_of_embryos_to_be_replaced</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Whole Number</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Cycle tab</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>Show / Hide</t>
         </is>
       </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>Binds to entity</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>Folliculogram</t>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>Drugs</t>
         </is>
       </c>
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>AppointmentDosage</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>Oocyte Retrieval</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_opu</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>Semen</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_semenprep</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>Lab Results</t>
         </is>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B40" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_eggdetail</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>Embryo Transfer</t>
         </is>
       </c>
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_embryotransfer</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>IUI/DI</t>
         </is>
       </c>
-      <c r="B42" s="18" t="inlineStr">
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_insemination</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Gametes</t>
         </is>
       </c>
-      <c r="B43" s="17" t="inlineStr">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_egg</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>Stored Sample</t>
         </is>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B44" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_egg / bcrm_cryolocation</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>Outcome Data</t>
         </is>
       </c>
-      <c r="B45" s="17" t="inlineStr">
+      <c r="B45" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_pregnancy_outcome_details</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>Checklists</t>
         </is>
       </c>
-      <c r="B46" s="17" t="inlineStr">
+      <c r="B46" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
+        </is>
+      </c>
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_consentchecklist</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1461,19 +2327,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Egg Only — Template Definition</t>
+          <t>Egg Only — Template Definition (UI binding)</t>
         </is>
       </c>
     </row>
@@ -1494,11 +2366,11 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Plan steps (seeds the worklist):</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>Plan steps (seed the worklist):</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Consent &amp; 3PC  →  Stimulation  →  Folliculogram  →  Trigger  →  OPU  →  Denuding / MII  →  Vitrify Oocytes  →  Storage</t>
@@ -1513,17 +2385,47 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Field shown</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Sample value (test couple)</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t>Attribute (logical)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Data type</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Relationship / Option set</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t>Required</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Sample value</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Src</t>
         </is>
       </c>
     </row>
@@ -1538,14 +2440,44 @@
           <t>Treatment Name</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_name</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Textbox</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Egg Freezing</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -1556,14 +2488,44 @@
           <t>Treatment Type</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmenttype</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet: bcrm_treatmenttype</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Egg Only</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -1574,12 +2536,42 @@
           <t>Cycle Sequence No</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_cyclesequencenumber</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>AutoNumber</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Read-only</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>CY-1184</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -1588,14 +2580,44 @@
           <t>Billing Option</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmentbillingoption</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Self-funded</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
@@ -1606,12 +2628,42 @@
           <t>ANZARD Cycle Type</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_anzardcycletype</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Stimulated — freeze all</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr"/>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr"/>
@@ -1620,12 +2672,42 @@
           <t>Treatment Template</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmenttemplate</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_eventtemplate</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Egg Freezing</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr"/>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -1638,14 +2720,44 @@
           <t>Patient</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_patient</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; contact</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Priya Sample (DEMO) · NHR-0042 · F · DOB 12 Mar 1991</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -1656,14 +2768,44 @@
           <t>Cycle Doctor</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_cycledoctor</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; systemuser/bcrm_staff</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Dr M. Osei</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
@@ -1674,12 +2816,42 @@
           <t>Cycle Nurse</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_cyclenurse</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; systemuser/bcrm_staff</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>R. Nolan</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr"/>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr"/>
@@ -1688,14 +2860,44 @@
           <t>Patient RX Group</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_patientrxgroup</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Group B</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
@@ -1710,12 +2912,42 @@
           <t>Managing Clinic</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_managingclinic</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; account/bcrm_clinic</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>OX.ar City (DEMO)</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr"/>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr"/>
@@ -1724,12 +2956,42 @@
           <t>Procedure Clinic</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_procedureclinic</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; account/bcrm_clinic</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>OX.ar City Lab</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr"/>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr"/>
@@ -1738,12 +3000,42 @@
           <t>Expected Start</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_expectedstartdate</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>14 Jul 2026</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr"/>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr"/>
@@ -1752,12 +3044,42 @@
           <t>First Injection</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_firstinjectiondate</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>1:1 stim detail</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>16 Jul 2026</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr"/>
@@ -1766,15 +3088,45 @@
           <t>Expected OPU</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_expectedtreatmentdate</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>28 Jul 2026</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr"/>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>Indication</t>
         </is>
@@ -1784,12 +3136,42 @@
           <t>Reason</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmentfeatures</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Multiline Text</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Textarea</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Elective fertility preservation</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr"/>
@@ -1798,15 +3180,45 @@
           <t>AMH Validated</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_amh_validated</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Two Options</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Toggle</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>Yes — 18.2 pmol/L</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr"/>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
@@ -1816,12 +3228,42 @@
           <t>Event Template</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_eventtemplate</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_eventtemplate (ApplyToCycle seeds events)</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Egg Freezing</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr"/>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr"/>
@@ -1830,12 +3272,42 @@
           <t>Research Project</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_researchproject</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_researchproject</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr"/>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr"/>
@@ -1844,12 +3316,42 @@
           <t>Freeze Method</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_freezeevent</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_freezemethod</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Vitrification</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr"/>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr"/>
@@ -1858,174 +3360,269 @@
           <t>Target eggs to store</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_targeteggstostore</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Textbox</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>≥ 10 MII</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr"/>
+      <c r="J29" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Cycle tab</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>Show / Hide</t>
         </is>
       </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>Binds to entity</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>Folliculogram</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Drugs</t>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>AppointmentDosage</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Oocyte Retrieval</t>
         </is>
       </c>
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_opu</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>Semen</t>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_semenprep</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>Lab Results</t>
         </is>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_eggdetail</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>Embryo Transfer</t>
         </is>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_embryotransfer</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>IUI/DI</t>
         </is>
       </c>
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_insemination</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>Gametes</t>
         </is>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B40" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_egg</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>Stored Sample</t>
         </is>
       </c>
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_egg / bcrm_cryolocation</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>Outcome Data</t>
         </is>
       </c>
-      <c r="B42" s="18" t="inlineStr">
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_pregnancy_outcome_details</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Checklists</t>
         </is>
       </c>
-      <c r="B43" s="17" t="inlineStr">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_consentchecklist</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2037,19 +3634,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Embryo Transfer — Template Definition</t>
+          <t>Embryo Transfer — Template Definition (UI binding)</t>
         </is>
       </c>
     </row>
@@ -2070,11 +3673,11 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Plan steps (seeds the worklist):</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>Plan steps (seed the worklist):</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Consent &amp; 3PC  →  Endometrial Prep / Lining  →  Select Embryo  →  Embryo Thaw  →  3PC  →  Transfer  →  Outcome</t>
@@ -2089,17 +3692,47 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Field shown</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Sample value (test couple)</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t>Attribute (logical)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Data type</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Relationship / Option set</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t>Required</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Sample value</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Src</t>
         </is>
       </c>
     </row>
@@ -2114,14 +3747,44 @@
           <t>Treatment Name</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_name</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Textbox</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>FET — Medicated</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -2132,14 +3795,44 @@
           <t>Treatment Type</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmenttype</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet: bcrm_treatmenttype</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Embryo Transfer</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -2150,12 +3843,42 @@
           <t>Cycle Sequence No</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_cyclesequencenumber</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>AutoNumber</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Read-only</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>CY-1185</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -2164,14 +3887,44 @@
           <t>Billing Option</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmentbillingoption</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Medicare + gap</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
@@ -2182,12 +3935,42 @@
           <t>ANZARD Cycle Type</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_anzardcycletype</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>FET</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr"/>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr"/>
@@ -2196,12 +3979,42 @@
           <t>Treatment Template</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmenttemplate</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_eventtemplate</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>FET (Frozen Embryo Transfer)</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr"/>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -2214,14 +4027,44 @@
           <t>Patient</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_patient</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; contact</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Priya Sample (DEMO) · NHR-0042 · F · DOB 12 Mar 1991</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -2232,12 +4075,42 @@
           <t>Partner</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_partner</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; contact</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Alex Sample (DEMO) · NHR-0043 · M · DOB 04 Aug 1988</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr"/>
@@ -2246,14 +4119,44 @@
           <t>Cycle Doctor</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_cycledoctor</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; systemuser/bcrm_staff</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Dr M. Osei</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
@@ -2264,12 +4167,42 @@
           <t>Cycle Nurse</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_cyclenurse</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; systemuser/bcrm_staff</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>R. Nolan</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr"/>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
@@ -2278,19 +4211,49 @@
           <t>Patient RX Group</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_patientrxgroup</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Group B</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Clinic &amp; Dates</t>
         </is>
@@ -2300,12 +4263,42 @@
           <t>Managing Clinic</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_managingclinic</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; account/bcrm_clinic</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>OX.ar City (DEMO)</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr"/>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr"/>
@@ -2314,12 +4307,42 @@
           <t>Lining Check</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_liningcheckdate</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>1:1 stim detail</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>22 Jul 2026</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr"/>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr"/>
@@ -2328,12 +4351,42 @@
           <t>Expected Transfer</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_expectedtreatmentdate</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>29 Jul 2026</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr"/>
+      <c r="J22" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -2346,12 +4399,42 @@
           <t>Event Template</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_eventtemplate</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_eventtemplate (ApplyToCycle seeds events)</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>FET</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr"/>
+      <c r="J23" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr"/>
@@ -2360,12 +4443,42 @@
           <t>Endometrial Prep</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_endometrialprep</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet (Medicated/Natural)</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Medicated (HRT)</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr"/>
@@ -2374,12 +4487,42 @@
           <t>Selected Embryo</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_embryotransfer</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_embryo</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_egg (embryo)</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>EMB-1042 · Blast 4AA · Day 5</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr"/>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr"/>
@@ -2388,174 +4531,269 @@
           <t>No. Embryos to Replace</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_no_of_embryos_to_be_replaced</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Whole Number</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Cycle tab</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>Show / Hide</t>
         </is>
       </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>Binds to entity</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>Folliculogram</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Drugs</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>AppointmentDosage</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>Oocyte Retrieval</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_opu</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>Semen</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_semenprep</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Lab Results</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_eggdetail</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Embryo Transfer</t>
         </is>
       </c>
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_embryotransfer</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>IUI/DI</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_insemination</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>Gametes</t>
         </is>
       </c>
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_egg</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>Stored Sample</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_egg / bcrm_cryolocation</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>Outcome Data</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_pregnancy_outcome_details</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>Checklists</t>
         </is>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B40" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_consentchecklist</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2567,19 +4805,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>VOT — Template Definition</t>
+          <t>VOT — Template Definition (UI binding)</t>
         </is>
       </c>
     </row>
@@ -2591,7 +4835,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Uses partner: Yes   ·   ⚠ VOT is a site-specific acronym — confirm exact meaning with MIVF/SME.</t>
         </is>
@@ -2600,11 +4844,11 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Plan steps (seeds the worklist):</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>Plan steps (seed the worklist):</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Consent &amp; 3PC  →  Select Frozen Eggs  →  Oocyte Thaw  →  Survival Check  →  Semen Prep  →  ICSI  →  Fertilisation  →  Culture  →  Transfer / Freeze  →  Outcome</t>
@@ -2619,17 +4863,47 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Field shown</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Sample value (test couple)</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t>Attribute (logical)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Data type</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Relationship / Option set</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t>Required</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Sample value</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Src</t>
         </is>
       </c>
     </row>
@@ -2644,14 +4918,44 @@
           <t>Treatment Name</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_name</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Textbox</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>VOT — thaw &amp; ICSI</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -2662,14 +4966,44 @@
           <t>Treatment Type</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmenttype</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet: bcrm_treatmenttype</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>VOT</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -2680,12 +5014,42 @@
           <t>Cycle Sequence No</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_cyclesequencenumber</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>AutoNumber</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Read-only</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>CY-1186</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -2694,14 +5058,44 @@
           <t>Billing Option</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmentbillingoption</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Self-funded</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
@@ -2712,12 +5106,42 @@
           <t>ANZARD Cycle Type</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_anzardcycletype</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Thaw oocytes</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr"/>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr"/>
@@ -2726,12 +5150,42 @@
           <t>Treatment Template</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmenttemplate</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_eventtemplate</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Vitrified Oocyte Thaw</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr"/>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -2744,14 +5198,44 @@
           <t>Patient</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_patient</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; contact</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Priya Sample (DEMO) · NHR-0042 · F · DOB 12 Mar 1991</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -2762,12 +5246,42 @@
           <t>Partner</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_partner</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; contact</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Alex Sample (DEMO) · NHR-0043 · M · DOB 04 Aug 1988</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr"/>
@@ -2776,14 +5290,44 @@
           <t>Cycle Doctor</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_cycledoctor</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; systemuser/bcrm_staff</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Dr M. Osei</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
@@ -2794,14 +5338,44 @@
           <t>Patient RX Group</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_patientrxgroup</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Group B</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
@@ -2816,12 +5390,42 @@
           <t>Managing Clinic</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_managingclinic</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; account/bcrm_clinic</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>OX.ar City (DEMO)</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr"/>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr"/>
@@ -2830,12 +5434,42 @@
           <t>Expected Thaw</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_thawevent</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_scheduledthawdate</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>1:N per cycle</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>26 Jul 2026</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr"/>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr"/>
@@ -2844,15 +5478,45 @@
           <t>Expected Transfer</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_expectedtreatmentdate</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>31 Jul 2026</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr"/>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
@@ -2862,12 +5526,42 @@
           <t>Event Template</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_eventtemplate</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_eventtemplate (ApplyToCycle seeds events)</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>VOT</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr"/>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr"/>
@@ -2876,12 +5570,42 @@
           <t>Frozen Oocytes to Thaw</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_thawevent</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_materialrecord</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_egg (oocyte)</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>6 (MII)</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr"/>
+      <c r="J23" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr"/>
@@ -2890,12 +5614,42 @@
           <t>Sperm Source</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_spermsource</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Partner (fresh)</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr"/>
@@ -2904,12 +5658,42 @@
           <t>Insemination Method</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_insemination</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_method</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>OptionSet (IVF/ICSI)</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>ICSI</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr"/>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr"/>
@@ -2918,174 +5702,269 @@
           <t>No. Embryos to Replace</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_no_of_embryos_to_be_replaced</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Whole Number</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Cycle tab</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>Show / Hide</t>
         </is>
       </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>Binds to entity</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>Folliculogram</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Drugs</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>AppointmentDosage</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>Oocyte Retrieval</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_opu</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>Semen</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_semenprep</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Lab Results</t>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_eggdetail</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Embryo Transfer</t>
         </is>
       </c>
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_embryotransfer</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>IUI/DI</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_insemination</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>Gametes</t>
         </is>
       </c>
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_egg</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>Stored Sample</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_egg / bcrm_cryolocation</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>Outcome Data</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_pregnancy_outcome_details</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>Checklists</t>
         </is>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B40" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_consentchecklist</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3097,19 +5976,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>IUI — Template Definition</t>
+          <t>IUI — Template Definition (UI binding)</t>
         </is>
       </c>
     </row>
@@ -3130,11 +6015,11 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Plan steps (seeds the worklist):</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>Plan steps (seed the worklist):</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Consent &amp; 3PC  →  OI / Natural  →  Folliculogram  →  Trigger  →  Semen Prep  →  IUI Insemination  →  Outcome</t>
@@ -3149,17 +6034,47 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Field shown</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Sample value (test couple)</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t>Attribute (logical)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Data type</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Relationship / Option set</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t>Required</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Sample value</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Src</t>
         </is>
       </c>
     </row>
@@ -3174,14 +6089,44 @@
           <t>Treatment Name</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_name</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Textbox</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>IUI — Natural cycle</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -3192,14 +6137,44 @@
           <t>Treatment Type</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmenttype</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet: bcrm_treatmenttype</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>IUI</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -3210,12 +6185,42 @@
           <t>Cycle Sequence No</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_cyclesequencenumber</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>AutoNumber</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Read-only</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>CY-1187</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -3224,14 +6229,44 @@
           <t>Billing Option</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmentbillingoption</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Self-funded</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
@@ -3242,12 +6277,42 @@
           <t>ANZARD Cycle Type</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_anzardcycletype</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>IUI</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr"/>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr"/>
@@ -3256,12 +6321,42 @@
           <t>Treatment Template</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmenttemplate</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_eventtemplate</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>IUI</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr"/>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -3274,14 +6369,44 @@
           <t>Patient</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_patient</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; contact</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Priya Sample (DEMO) · NHR-0042 · F · DOB 12 Mar 1991</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -3292,12 +6417,42 @@
           <t>Partner</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_partner</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; contact</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Alex Sample (DEMO) · NHR-0043 · M · DOB 04 Aug 1988</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr"/>
@@ -3306,14 +6461,44 @@
           <t>Cycle Doctor</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_cycledoctor</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; systemuser/bcrm_staff</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Dr M. Osei</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
@@ -3324,12 +6509,42 @@
           <t>Cycle Nurse</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_cyclenurse</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; systemuser/bcrm_staff</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>R. Nolan</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr"/>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
@@ -3338,19 +6553,49 @@
           <t>Patient RX Group</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_patientrxgroup</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Group A</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Clinic &amp; Dates</t>
         </is>
@@ -3360,12 +6605,42 @@
           <t>Managing Clinic</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_managingclinic</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; account/bcrm_clinic</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>OX.ar City (DEMO)</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr"/>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr"/>
@@ -3374,12 +6649,42 @@
           <t>LH Surge</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_lhsurgedate</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>1:1 stim detail</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>24 Jul 2026</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr"/>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr"/>
@@ -3388,12 +6693,42 @@
           <t>Expected Insemination</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_insemination</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_date</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>1:N per cycle</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>25 Jul 2026</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr"/>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -3406,12 +6741,42 @@
           <t>Female Diagnosis</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_details_diagnosis</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>OptionSet / Lookup</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Unexplained</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr"/>
@@ -3420,12 +6785,42 @@
           <t>Male Diagnosis</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_details_sec_diagnosis</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet / Lookup</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Normal parameters</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -3438,12 +6833,42 @@
           <t>Event Template</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_eventtemplate</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_eventtemplate (ApplyToCycle seeds events)</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>IUI</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr"/>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr"/>
@@ -3452,12 +6877,42 @@
           <t>Sperm Source</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_spermsource</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Partner (prepared)</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr"/>
@@ -3466,12 +6921,42 @@
           <t>Prepared Motile Count</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_semenprep</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_count</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>18 M/mL</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr"/>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr"/>
@@ -3480,174 +6965,269 @@
           <t>Trigger</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_timeoftrigger</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>hCG</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Cycle tab</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>Show / Hide</t>
         </is>
       </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>Binds to entity</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>Folliculogram</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>Drugs</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>AppointmentDosage</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Oocyte Retrieval</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_opu</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Semen</t>
         </is>
       </c>
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_semenprep</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>Lab Results</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_eggdetail</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>Embryo Transfer</t>
         </is>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_embryotransfer</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>IUI/DI</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_insemination</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>Gametes</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_egg</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>Stored Sample</t>
         </is>
       </c>
-      <c r="B40" s="18" t="inlineStr">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_egg / bcrm_cryolocation</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>Outcome Data</t>
         </is>
       </c>
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_pregnancy_outcome_details</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>Checklists</t>
         </is>
       </c>
-      <c r="B42" s="17" t="inlineStr">
+      <c r="B42" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_consentchecklist</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3659,19 +7239,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Ovulation Induction — Template Definition</t>
+          <t>Ovulation Induction — Template Definition (UI binding)</t>
         </is>
       </c>
     </row>
@@ -3692,11 +7278,11 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Plan steps (seeds the worklist):</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>Plan steps (seed the worklist):</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Consent  →  OI Drugs  →  Folliculogram  →  Trigger  →  Timed Intercourse  →  Outcome</t>
@@ -3711,17 +7297,47 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Field shown</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Sample value (test couple)</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t>Attribute (logical)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Data type</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Relationship / Option set</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t>Required</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Sample value</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Src</t>
         </is>
       </c>
     </row>
@@ -3736,14 +7352,44 @@
           <t>Treatment Name</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_name</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Textbox</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Ovulation Induction — Letrozole</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -3754,14 +7400,44 @@
           <t>Treatment Type</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmenttype</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet: bcrm_treatmenttype</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Ovulation Induction</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -3772,12 +7448,42 @@
           <t>Cycle Sequence No</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_cyclesequencenumber</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>AutoNumber</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Read-only</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>CY-1188</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -3786,14 +7492,44 @@
           <t>Billing Option</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmentbillingoption</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Self-funded</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
@@ -3804,15 +7540,45 @@
           <t>Treatment Template</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatmenttemplate</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_eventtemplate</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Ovulation Induction</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr"/>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>People</t>
         </is>
@@ -3822,14 +7588,44 @@
           <t>Patient</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_patient</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; contact</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Priya Sample (DEMO) · NHR-0042 · F · DOB 12 Mar 1991</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -3840,14 +7636,44 @@
           <t>Cycle Doctor</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_cycledoctor</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; systemuser/bcrm_staff</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Dr M. Osei</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
         </is>
       </c>
     </row>
@@ -3858,12 +7684,42 @@
           <t>Cycle Nurse</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_cyclenurse</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; systemuser/bcrm_staff</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>R. Nolan</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr"/>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -3876,12 +7732,42 @@
           <t>Managing Clinic</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_managingclinic</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; account/bcrm_clinic</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>OX.ar City (DEMO)</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr"/>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr"/>
@@ -3890,12 +7776,42 @@
           <t>Baseline Scan</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_dateofbaselinescan</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>1:1 stim detail</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>14 Jul 2026</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
@@ -3904,15 +7820,45 @@
           <t>Day-10 Scan</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_day10scandate</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>1:1 stim detail</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>24 Jul 2026</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr"/>
+      <c r="J19" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Infertility Diagnosis</t>
         </is>
@@ -3922,12 +7868,42 @@
           <t>Female Diagnosis</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_details_diagnosis</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet / Lookup</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>PCOS — anovulation</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -3940,12 +7916,42 @@
           <t>Drug</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>AppointmentDosage</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_drug</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Lookup / Text</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>1:N drug rows</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Letrozole 5 mg (days 3-7)</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr"/>
@@ -3954,12 +7960,42 @@
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_folliculogram_comments</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Multiline Text</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Textarea</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>Serial follicle scans</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr"/>
@@ -3968,174 +8004,269 @@
           <t>Trigger</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_timeoftrigger</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>hCG when lead follicle ≥ 18 mm</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Cycle tab</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>Show / Hide</t>
         </is>
       </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>Binds to entity</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Folliculogram</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>Drugs</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>AppointmentDosage</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Oocyte Retrieval</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_opu</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>Semen</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_semenprep</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Lab Results</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_eggdetail</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>Embryo Transfer</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_embryotransfer</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>IUI/DI</t>
         </is>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_insemination</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Gametes</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_egg</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Stored Sample</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_egg / bcrm_cryolocation</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>Outcome Data</t>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_pregnancy_outcome_details</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>Checklists</t>
         </is>
       </c>
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_consentchecklist</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4147,19 +8278,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Tracking — Template Definition</t>
+          <t>Tracking — Template Definition (UI binding)</t>
         </is>
       </c>
     </row>
@@ -4180,11 +8317,11 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Plan steps (seeds the worklist):</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>Plan steps (seed the worklist):</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Folliculogram Tracking  →  LH &amp; Trigger Monitoring  →  Outcome / Hand-off</t>
@@ -4199,17 +8336,47 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Field shown</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Sample value (test couple)</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t>Attribute (logical)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Data type</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Relationship / Option set</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t>Required</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Sample value</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Src</t>
         </is>
       </c>
     </row>
@@ -4224,14 +8391,44 @@
           <t>Treatment Name</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_name</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Textbox</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Cycle Tracking</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -4242,14 +8439,44 @@
           <t>Treatment Type</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmenttype</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet: bcrm_treatmenttype</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Tracking</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -4260,12 +8487,42 @@
           <t>Cycle Sequence No</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_cyclesequencenumber</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>AutoNumber</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Read-only</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>CY-1189</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -4274,12 +8531,42 @@
           <t>Treatment Template</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmenttemplate</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_eventtemplate</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Cycle Tracking</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr"/>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -4292,14 +8579,44 @@
           <t>Patient</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_patient</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; contact</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Priya Sample (DEMO) · NHR-0042 · F · DOB 12 Mar 1991</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -4310,12 +8627,42 @@
           <t>Cycle Doctor</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_cycledoctor</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; systemuser/bcrm_staff</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Dr M. Osei</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr"/>
+      <c r="J14" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr"/>
@@ -4324,15 +8671,45 @@
           <t>Cycle Nurse</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_cyclenurse</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; systemuser/bcrm_staff</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>R. Nolan</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr"/>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Clinic &amp; Dates</t>
         </is>
@@ -4342,12 +8719,42 @@
           <t>Managing Clinic</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_managingclinic</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; account/bcrm_clinic</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>OX.ar City (DEMO)</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr"/>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr"/>
@@ -4356,12 +8763,42 @@
           <t>Period Started</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_expecteddateperiodstarted</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>10 Jul 2026</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr"/>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr"/>
@@ -4370,12 +8807,42 @@
           <t>Actual Period Date</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_actualperioddate</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Date picker</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>10 Jul 2026</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr"/>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -4388,12 +8855,42 @@
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_folliculogram_comments</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Multiline Text</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Textarea</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Serial scans + LH</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr"/>
@@ -4402,174 +8899,269 @@
           <t>Hand-off</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_handoffnote</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Multiline Text</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Textarea</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>to IUI / IVF if indicated</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr"/>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Cycle tab</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Show / Hide</t>
         </is>
       </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>Binds to entity</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Folliculogram</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Drugs</t>
         </is>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>AppointmentDosage</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>Oocyte Retrieval</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_opu</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Semen</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_semenprep</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>Lab Results</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_eggdetail</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Embryo Transfer</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_embryotransfer</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>IUI/DI</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_insemination</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Gametes</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_egg</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>Stored Sample</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_egg / bcrm_cryolocation</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>Outcome Data</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_pregnancy_outcome_details</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Checklists</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_consentchecklist</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4581,19 +9173,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Thaw and Refreeze — Template Definition</t>
+          <t>Thaw and Refreeze — Template Definition (UI binding)</t>
         </is>
       </c>
     </row>
@@ -4614,11 +9212,11 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Plan steps (seeds the worklist):</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>Plan steps (seed the worklist):</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Consent &amp; 3PC  →  Select Specimen  →  Thaw  →  Assess (± Biopsy)  →  Refreeze  →  Storage  →  Witnessing</t>
@@ -4633,17 +9231,47 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Field shown</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Sample value (test couple)</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t>Attribute (logical)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Data type</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Relationship / Option set</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t>Required</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Sample value</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Src</t>
         </is>
       </c>
     </row>
@@ -4658,14 +9286,44 @@
           <t>Treatment Name</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_name</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Textbox</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Thaw &amp; Refreeze — PGT</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -4676,14 +9334,44 @@
           <t>Treatment Type</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmenttype</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>OptionSet: bcrm_treatmenttype</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Thaw and Refreeze</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -4694,12 +9382,42 @@
           <t>Cycle Sequence No</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_cyclesequencenumber</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>AutoNumber</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Read-only</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>CY-1190</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>form</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -4708,12 +9426,42 @@
           <t>Treatment Template</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmenttemplate</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_eventtemplate</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Thaw and Refreeze</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr"/>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -4726,14 +9474,44 @@
           <t>Patient</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_patient</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; contact</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Priya Sample (DEMO) · NHR-0042 · F · DOB 12 Mar 1991</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
         </is>
       </c>
     </row>
@@ -4744,12 +9522,42 @@
           <t>Partner</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_partner</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; contact</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Alex Sample (DEMO) · NHR-0043 · M · DOB 04 Aug 1988</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr"/>
@@ -4758,14 +9566,44 @@
           <t>Embryologist</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_thawevent</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_embryologist</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; systemuser/bcrm_staff</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>A. Kaur</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J15" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
@@ -4776,14 +9614,44 @@
           <t>Witness</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_thawevent</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_witness</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; systemuser/bcrm_staff (independent)</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>R. Nolan</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
     </row>
@@ -4798,12 +9666,42 @@
           <t>Specimen</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_egg</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_eggs_id</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_egg</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>EMB-1043 · Blast 3BB</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr"/>
+      <c r="J17" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr"/>
@@ -4812,12 +9710,42 @@
           <t>Reason</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_treatmentfeatures</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Multiline Text</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Textarea</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Biopsy for PGT-A</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
@@ -4826,12 +9754,42 @@
           <t>Refreeze Method</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_freezeevent</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>bcrm_freezemethod</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>OptionSet</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Vitrification</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr"/>
+      <c r="J19" s="18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr"/>
@@ -4840,174 +9798,269 @@
           <t>Storage Location</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_cryolocation</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>bcrm_cryolocationid</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>N:1 -&gt; bcrm_cryolocation</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>TANK-01 · C1 · G2 · S5</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr"/>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Cycle tab</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Show / Hide</t>
         </is>
       </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>Binds to entity</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_treatment_cycle</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Folliculogram</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_fertilitytreatment</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Drugs</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>AppointmentDosage</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>Oocyte Retrieval</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_opu</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Semen</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_semenprep</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>Lab Results</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_eggdetail</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Embryo Transfer</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_embryotransfer</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>IUI/DI</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_insemination</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Gametes</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_egg</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>Stored Sample</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
         </is>
       </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_egg / bcrm_cryolocation</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>Outcome Data</t>
         </is>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>HIDE</t>
         </is>
       </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_pregnancy_outcome_details</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Checklists</t>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>SHOW</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>bcrm_consentchecklist</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
